--- a/data/trans_camb/P2A_fisi_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,99</t>
+          <t>1,9; 7,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,91</t>
+          <t>-2,49; 2,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 18,59</t>
+          <t>10,58; 18,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,93</t>
+          <t>0,97; 6,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,48</t>
+          <t>0,65; 6,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,82; 16,45</t>
+          <t>11,18; 16,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,05</t>
+          <t>2,33; 5,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,77</t>
+          <t>0,24; 3,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,97; 16,5</t>
+          <t>12,02; 16,19</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,32; 110,76</t>
+          <t>21,48; 108,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,8; 41,62</t>
+          <t>-26,78; 40,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113,98; 263,14</t>
+          <t>113,35; 270,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 70,44</t>
+          <t>8,81; 73,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 75,44</t>
+          <t>4,83; 68,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,71; 191,67</t>
+          <t>103,65; 199,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,69; 73,01</t>
+          <t>23,74; 71,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 45,52</t>
+          <t>2,37; 48,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>121,66; 202,4</t>
+          <t>121,41; 196,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,02</t>
+          <t>0,18; 2,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,78</t>
+          <t>-0,03; 2,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,97</t>
+          <t>2,48; 6,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,95</t>
+          <t>1,63; 5,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,36</t>
+          <t>-0,78; 2,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 36,79</t>
+          <t>3,79; 34,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,27</t>
+          <t>1,19; 3,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,04</t>
+          <t>0,08; 2,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 22,75</t>
+          <t>4,11; 22,73</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 97,18</t>
+          <t>3,48; 96,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 86,55</t>
+          <t>-1,75; 81,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,75; 216,95</t>
+          <t>62,5; 213,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,73; 148,67</t>
+          <t>33,54; 157,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 74,27</t>
+          <t>-15,72; 67,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,1; 1103,63</t>
+          <t>92,39; 1017,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,3; 99,73</t>
+          <t>26,95; 100,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 58,94</t>
+          <t>1,06; 58,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>105,1; 662,07</t>
+          <t>103,18; 626,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,64</t>
+          <t>-1,32; 3,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,85</t>
+          <t>-1,52; 3,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,4</t>
+          <t>1,48; 7,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 3,26</t>
+          <t>-2,68; 3,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,85</t>
+          <t>-3,78; 1,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,64</t>
+          <t>-2,58; 2,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,61</t>
+          <t>-1,26; 2,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,78</t>
+          <t>-1,67; 1,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,23</t>
+          <t>0,64; 4,24</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 186,33</t>
+          <t>-38,79; 193,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,32; 163,52</t>
+          <t>-41,49; 178,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,35; 395,77</t>
+          <t>22,99; 365,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 103,68</t>
+          <t>-44,39; 98,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 57,79</t>
+          <t>-57,71; 52,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,5; 77,05</t>
+          <t>-36,9; 80,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 93,31</t>
+          <t>-32,53; 79,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,82; 59,57</t>
+          <t>-35,03; 60,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,21; 147,6</t>
+          <t>10,32; 155,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,69</t>
+          <t>1,16; 3,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,67</t>
+          <t>-0,64; 1,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,11</t>
+          <t>3,05; 6,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,17</t>
+          <t>1,56; 4,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,78</t>
+          <t>-0,53; 1,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,2; 25,31</t>
+          <t>4,36; 25,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,44</t>
+          <t>1,71; 3,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,39</t>
+          <t>-0,2; 1,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 17,21</t>
+          <t>4,7; 17,24</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,8; 81,36</t>
+          <t>20,24; 78,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 37,38</t>
+          <t>-11,57; 35,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62,09; 159,59</t>
+          <t>62,08; 153,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,92; 72,79</t>
+          <t>22,4; 77,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 31,58</t>
+          <t>-7,84; 34,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,35; 427,44</t>
+          <t>66,34; 436,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,87; 66,64</t>
+          <t>27,85; 67,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 26,55</t>
+          <t>-3,35; 27,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>78,87; 304,64</t>
+          <t>81,35; 304,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,37</t>
+          <t>13,04</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,92</t>
+          <t>14,06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,15</t>
+          <t>13,68</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,7</t>
+          <t>2,1; 7,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,87</t>
+          <t>-2,45; 3,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 18,51</t>
+          <t>9,76; 16,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,13</t>
+          <t>0,83; 6,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,32</t>
+          <t>0,58; 6,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 16,75</t>
+          <t>11,37; 17,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,96</t>
+          <t>2,12; 5,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,96</t>
+          <t>-0,09; 4,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,02; 16,19</t>
+          <t>11,38; 15,85</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>174,54%</t>
+          <t>158,42%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>144,85%</t>
+          <t>146,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>157,14%</t>
+          <t>151,88%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,48; 108,2</t>
+          <t>20,03; 113,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 40,29</t>
+          <t>-26,28; 43,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113,35; 270,04</t>
+          <t>101,59; 236,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 73,82</t>
+          <t>7,66; 73,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 68,52</t>
+          <t>4,94; 70,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>103,65; 199,81</t>
+          <t>103,85; 202,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,74; 71,98</t>
+          <t>22,04; 71,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 48,25</t>
+          <t>-0,96; 48,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>121,41; 196,27</t>
+          <t>114,32; 193,56</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,69</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,8</t>
+          <t>5,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,97</t>
+          <t>0,15; 2,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,63</t>
+          <t>-0,09; 2,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,89</t>
+          <t>4,25; 7,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,1</t>
+          <t>1,73; 4,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,17</t>
+          <t>-0,59; 2,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 34,31</t>
+          <t>3,55; 6,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,37</t>
+          <t>1,32; 3,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,0</t>
+          <t>0,06; 1,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 22,73</t>
+          <t>4,31; 6,4</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133,61%</t>
+          <t>152,96%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>324,47%</t>
+          <t>126,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>230,19%</t>
+          <t>139,53%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 96,53</t>
+          <t>1,31; 94,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 81,95</t>
+          <t>-2,28; 83,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,5; 213,0</t>
+          <t>96,86; 238,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,54; 157,83</t>
+          <t>33,6; 147,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 67,92</t>
+          <t>-12,59; 68,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,39; 1017,09</t>
+          <t>74,05; 210,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,95; 100,68</t>
+          <t>31,26; 105,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 58,6</t>
+          <t>1,98; 60,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>103,18; 626,5</t>
+          <t>98,46; 191,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,24</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,79</t>
+          <t>-1,39; 3,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,27</t>
+          <t>-1,59; 3,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,13</t>
+          <t>1,35; 6,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,35</t>
+          <t>-2,63; 3,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 1,85</t>
+          <t>-3,71; 1,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,64</t>
+          <t>-1,96; 2,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,41</t>
+          <t>-1,23; 2,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,64</t>
+          <t>-1,71; 1,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,24</t>
+          <t>0,62; 4,22</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152,67%</t>
+          <t>150,15%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 193,53</t>
+          <t>-38,05; 194,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 178,51</t>
+          <t>-39,79; 192,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,99; 365,43</t>
+          <t>26,09; 395,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,39; 98,99</t>
+          <t>-43,67; 98,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-57,71; 52,81</t>
+          <t>-56,31; 54,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 80,74</t>
+          <t>-30,98; 85,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 79,65</t>
+          <t>-28,92; 93,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 60,9</t>
+          <t>-37,38; 63,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,32; 155,83</t>
+          <t>7,49; 142,44</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,71</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,67</t>
+          <t>5,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,48</t>
+          <t>1,13; 3,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,65</t>
+          <t>-0,56; 1,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,98</t>
+          <t>4,64; 7,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,36</t>
+          <t>1,37; 4,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,92</t>
+          <t>-0,55; 1,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 25,58</t>
+          <t>3,86; 6,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,51</t>
+          <t>1,76; 3,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,42</t>
+          <t>-0,21; 1,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 17,24</t>
+          <t>4,67; 6,37</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>110,01%</t>
+          <t>118,24%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>155,13%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>136,08%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,24; 78,66</t>
+          <t>20,67; 78,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 35,89</t>
+          <t>-10,27; 39,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62,08; 153,41</t>
+          <t>82,4; 163,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,4; 77,5</t>
+          <t>19,71; 70,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 34,89</t>
+          <t>-8,54; 33,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,34; 436,21</t>
+          <t>54,53; 110,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,85; 67,86</t>
+          <t>28,92; 65,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 27,8</t>
+          <t>-3,33; 25,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>81,35; 304,77</t>
+          <t>75,97; 122,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
